--- a/OSBAMS_Pi_Power_Interposer_RevA_RC1/bom/OSBAMS_Pi_Power_Interposer_RevA_RC1_BOM.xlsx
+++ b/OSBAMS_Pi_Power_Interposer_RevA_RC1/bom/OSBAMS_Pi_Power_Interposer_RevA_RC1_BOM.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -583,29 +583,64 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>M1, M2</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>M2.5 standoff/spacer + screw to the Pi header-end mounting holes; spacer length = seated height of the chosen stacking socket</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>NPTH 2.7 mm</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>OPEN - depends on socket MPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>Harness</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Micro-Fit receptacle housing 43025-0400 at both ends (candidate), 4x 16 AWG, &lt;=150 mm, crimped, 43030-family terminals</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Molex</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>43025-0400 + 43030 (candidate)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>OPEN - confirm terminal for 16 AWG; strain relief (cable tie / clip)</t>
         </is>

--- a/OSBAMS_Pi_Power_Interposer_RevA_RC1/bom/OSBAMS_Pi_Power_Interposer_RevA_RC1_BOM.xlsx
+++ b/OSBAMS_Pi_Power_Interposer_RevA_RC1/bom/OSBAMS_Pi_Power_Interposer_RevA_RC1_BOM.xlsx
@@ -521,27 +521,27 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2x20 2.54 mm gold STACKING female header (Pi GPIO), &gt;=3 A/contact, long tails so Pi pins stay reachable for the Waveshare leads</t>
+          <t>Samtec SSW-120-01-S-D: 2x20, 2.54 mm, through-hole vertical receptacle, 30 uin gold / tin tails, body 8.51 mm, tail 2.64 mm, 4.7 A (one pin powered per row). Mounted from the UNDERSIDE, soldered from the top.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Samtec</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>SSW-120-01-S-D</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>OSBAMS_PiPwr:PinSocket_2x20_P2.54mm_RPi_TopView (pad pattern by Pi pin number)</t>
+          <t>OSBAMS_PiPwr:SSW-120-01-S-D_RPi_TopView (pad pattern by Pi pin number, 1.0 mm drill - confirm vs Samtec footprint)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>OPEN - exact MPN with published per-contact current/resistance must be chosen from a datasheet</t>
+          <t>Owner-selected; ordering code/dimensions to re-check vs the SSW-120 product page. Do NOT use SSW-120-04-G-D (14.83 mm tail, no stock)</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>M2.5 key standoffs/posts (outward side) - length set by the 3D check so a 180-degree fitting cannot seat</t>
+          <t>M2.5 female-female hex standoff, 20 mm (key posts, outward side) + M2.5 screws - length from check_stack_height.py</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M2.5 x 20 mm standoff</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>OPEN - 3D check vs Pi 5 drawing + enclosure</t>
+          <t>Length computed: socket face stays 11.5 mm above the Pi PCB when reversed (pin tips ~9 mm)</t>
         </is>
       </c>
     </row>
@@ -591,17 +591,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>M2.5 standoff/spacer + screw to the Pi header-end mounting holes; spacer length = seated height of the chosen stacking socket</t>
+          <t>M2.5 female-female hex standoff, 11 mm (= 8.51 mm socket body + ~2.5 mm Pi header plastic) + M2.5 screws, to the Pi header-end mounting holes</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M2.5 x 11 mm standoff</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>OPEN - depends on socket MPN</t>
+          <t>Standard HAT spacer length; confirm on a physical Pi 5</t>
         </is>
       </c>
     </row>

--- a/OSBAMS_Pi_Power_Interposer_RevA_RC1/bom/OSBAMS_Pi_Power_Interposer_RevA_RC1_BOM.xlsx
+++ b/OSBAMS_Pi_Power_Interposer_RevA_RC1/bom/OSBAMS_Pi_Power_Interposer_RevA_RC1_BOM.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Owner-selected; ordering code/dimensions to re-check vs the SSW-120 product page. Do NOT use SSW-120-04-G-D (14.83 mm tail, no stock)</t>
+          <t>Dimensions CONFIRMED by Samtec catalog F-226 (8.51 mm body, lead style -01 = 2.64 mm tail). PLATING LETTER MISMATCH: catalog plating codes are -F/-L (10 uin Au)/-G (20 uin Au)/-T; -S is a row option there. Confirm the orderable code (owner: SSW-120-01-S-D) with the distributor, or order SSW-120-01-L-D / -G-D. Do NOT use SSW-120-04-G-D (14.83 mm tail, no stock)</t>
         </is>
       </c>
     </row>
